--- a/healthcare_forms/027_health_evaluation_form--healthcare_forms.xlsx
+++ b/healthcare_forms/027_health_evaluation_form--healthcare_forms.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,13 +427,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -510,18 +510,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>patient_history</t>
+          <t>patient_history_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>patient_history</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Patient's medical history</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please describe your medical history, including any previous illnesses or allergies.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -533,15 +537,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>patient_lifestyle</t>
+          <t>patient_lifestyle_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>patient_lifestyle</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Patient's lifestyle habits</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Please describe your daily exercise routine, diet, and sleep patterns.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>no</t>
@@ -556,18 +564,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>patient_history</t>
+          <t>health_status</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>patient_history</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Patient's current health status</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Please provide a brief description of your current health status.</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -579,15 +591,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>patient_lifestyle</t>
+          <t>medical_services_1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>patient_lifestyle</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Medical services received in the past year</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>List any hospital stays or doctor visits in the past year.</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>no</t>
@@ -602,15 +618,19 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>patient_history</t>
+          <t>customize_form</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>patient_history</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Form customization</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Would you like to add or remove questions from this form?</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>no</t>
@@ -625,15 +645,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>patient_lifestyle</t>
+          <t>medical_history_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>patient_lifestyle</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Patient's previous illnesses</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>List any previous illnesses or allergies you've had.</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>no</t>
@@ -648,18 +672,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>patient_lifestyle</t>
+          <t>exercise_habits</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>patient_lifestyle</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Exercise habits</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Describe your exercise routine, including frequency and intensity.</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -671,15 +699,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>patient_history</t>
+          <t>health_services_1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>patient_history</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Medical services received</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>List any medical services you've received in the past year.</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
@@ -694,18 +726,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>healthcare_services</t>
+          <t>diet_patterns</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>healthcare_services</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Diet and nutrition</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Describe your diet and nutrition habits, including any supplements.</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -717,15 +753,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>customize_form</t>
+          <t>medical_services_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>customize_form</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Medical Services 2</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>List any additional medical services you've received in the past year.</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>no</t>
@@ -740,18 +780,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>patient_lifestyle</t>
+          <t>medical_status</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>patient_lifestyle</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Current health status</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Please provide a brief description of your current health status.</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -768,10 +812,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>healthcare_services</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Healthcare services received</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>List any healthcare services you've received in the past year.</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
@@ -786,15 +834,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>healthcare_services</t>
+          <t>medical_services_3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>healthcare_services</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>Medical Services 3</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>List any additional medical services you've received in the past year.</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>no</t>
@@ -809,18 +861,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>patient_history</t>
+          <t>health_status_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>patient_history</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>Health Status 2</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Please provide a brief description of your current health status.</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -832,15 +888,19 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>patient_lifestyle</t>
+          <t>healthcare_services_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>patient_lifestyle</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>Healthcare Services 2</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>List any additional healthcare services you've received in the past year.</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>no</t>
@@ -855,15 +915,19 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>healthcare_services</t>
+          <t>medical_history</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>healthcare_services</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>Medical history</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>List any previous illnesses or allergies you've had.</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>no</t>
@@ -878,18 +942,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>patient_history</t>
+          <t>health_status_2_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>patient_history</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>Health Status 2 2</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Please provide a brief description of your current health status.</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -901,177 +969,20 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>patient_lifestyle</t>
+          <t>healthcare_services_3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>patient_lifestyle</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>Healthcare Services 3</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>List any additional healthcare services you've received in the past year.</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>healthcare_services</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>healthcare_services</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>patient_history</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>patient_history</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>patient_lifestyle</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>patient_lifestyle</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>healthcare_services</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>healthcare_services</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>patient_history</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>patient_history</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>patient_lifestyle</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>patient_lifestyle</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>healthcare_services</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>healthcare_services</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
